--- a/branches/dev/v2027/StructureDefinition-mii-pr-patho-composition.xlsx
+++ b/branches/dev/v2027/StructureDefinition-mii-pr-patho-composition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T13:18:58+00:00</t>
+    <t>2026-09-01T13:59:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/v2027/StructureDefinition-mii-pr-patho-composition.xlsx
+++ b/branches/dev/v2027/StructureDefinition-mii-pr-patho-composition.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc</t>
+    <t>2027.0.0-ballot.rc1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T13:59:06+00:00</t>
+    <t>2026-09-03T08:45:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/v2027/StructureDefinition-mii-pr-patho-composition.xlsx
+++ b/branches/dev/v2027/StructureDefinition-mii-pr-patho-composition.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc1</t>
+    <t>2027.0.0-ballot.rc2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T08:45:38+00:00</t>
+    <t>2026-09-08T11:58:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/v2027/StructureDefinition-mii-pr-patho-composition.xlsx
+++ b/branches/dev/v2027/StructureDefinition-mii-pr-patho-composition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T11:58:20+00:00</t>
+    <t>2026-09-08T12:58:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/v2027/StructureDefinition-mii-pr-patho-composition.xlsx
+++ b/branches/dev/v2027/StructureDefinition-mii-pr-patho-composition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T12:58:28+00:00</t>
+    <t>2026-09-08T14:07:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/v2027/StructureDefinition-mii-pr-patho-composition.xlsx
+++ b/branches/dev/v2027/StructureDefinition-mii-pr-patho-composition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T14:07:59+00:00</t>
+    <t>2026-09-08T14:30:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
